--- a/healthcare_forms/013_wellness_center_invite_form--healthcare_forms.xlsx
+++ b/healthcare_forms/013_wellness_center_invite_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact_method_other</t>
+          <t>contact_method_other_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other Contact Method</t>
+          <t>Contact Method Other 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>contact_method_other</t>
+          <t>contact_method_other_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other Contact Method</t>
+          <t>Contact Method Other 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1148,46 +1148,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1262,34 +1262,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
